--- a/Polar Histogram.xlsx
+++ b/Polar Histogram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arrowstreamanalytics-my.sharepoint.com/personal/andrew_arrowstream_co_uk/Documents/Documents/GitHub/python-in-excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C30D3A56-8701-434C-B0C5-31A16A17B77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C30D3A56-8701-434C-B0C5-31A16A17B77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0791242-2714-417D-BFEE-007C729458DE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9BC2B87-9D9A-4EF2-9DDA-C83C2160BF53}"/>
   </bookViews>
@@ -122,7 +122,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -979,15 +979,15 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1090,13 +1090,7 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="35">
-          <cell r="C35">
-            <v>70</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
@@ -1700,52 +1694,52 @@
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="31.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="88.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="37.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+    <col min="6" max="6" width="88.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="37.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="e" vm="1">
+      <c r="B2" s="6" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="4" spans="2:9" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="2:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="2:9" ht="79.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
@@ -1754,117 +1748,117 @@
       <c r="C10" s="7"/>
     </row>
     <row r="12" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="210" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C13" s="2" cm="1" vm="2">
+      <c r="C13" s="1" cm="1" vm="2">
         <f t="array" ref="C13">_xlfn._xlws.PY(0,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="2" t="e" cm="1" vm="3">
+      <c r="C15" s="1" t="e" cm="1" vm="3">
         <f t="array" ref="C15">_xlfn._xlws.PY(1,1,data[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="180" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="2" cm="1" vm="2">
+      <c r="C17" s="1" cm="1" vm="2">
         <f t="array" ref="C17">_xlfn._xlws.PY(2,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="240" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="2" cm="1" vm="4">
+      <c r="C19" s="1" cm="1" vm="4">
         <f t="array" ref="C19">_xlfn._xlws.PY(3,1)</f>
         <v>16.4177</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="2" cm="1" vm="2">
+      <c r="C21" s="1" cm="1" vm="2">
         <f t="array" ref="C21">_xlfn._xlws.PY(4,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="240" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="2" cm="1" vm="2">
+      <c r="C23" s="1" cm="1" vm="2">
         <f t="array" ref="C23">_xlfn._xlws.PY(5,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="240" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="2" cm="1" vm="2">
+      <c r="C25" s="1" cm="1" vm="2">
         <f t="array" ref="C25">_xlfn._xlws.PY(6,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="255" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C27" s="2" cm="1" vm="2">
+      <c r="C27" s="1" cm="1" vm="2">
         <f t="array" ref="C27">_xlfn._xlws.PY(7,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="255" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C29" s="2" cm="1" vm="2">
+      <c r="C29" s="1" cm="1" vm="2">
         <f t="array" ref="C29">_xlfn._xlws.PY(8,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="120" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C31" s="2" cm="1" vm="2">
+      <c r="C31" s="1" cm="1" vm="2">
         <f t="array" ref="C31">_xlfn._xlws.PY(9,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="135" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="2" cm="1" vm="2">
+      <c r="C33" s="1" cm="1" vm="2">
         <f t="array" ref="C33">_xlfn._xlws.PY(10,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C35" s="2" t="e" cm="1" vm="5">
+      <c r="C35" s="1" t="e" cm="1" vm="5">
         <f t="array" ref="C35">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -1893,1607 +1887,1607 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>7.8209999999999997</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>7.6360000000000001</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>7.5570000000000004</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>7.5119999999999996</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>7.415</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>7.4039999999999999</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>7.3840000000000003</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>7.3650000000000002</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>7.3639999999999999</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>7.2</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>7.1630000000000003</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>7.1619999999999999</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>7.0410000000000004</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>7.0339999999999998</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>7.0250000000000004</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>6.9770000000000003</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>6.9429999999999996</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>6.92</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>6.8049999999999997</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>6.6870000000000003</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>6.6470000000000002</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>6.63</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>6.5819999999999999</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>6.5759999999999996</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="1">
         <v>6.5229999999999997</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="1">
         <v>6.5119999999999996</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="1">
         <v>6.48</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="1">
         <v>6.4770000000000003</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="1">
         <v>6.476</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="1">
         <v>6.4740000000000002</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="1">
         <v>6.4669999999999996</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="1">
         <v>6.4550000000000001</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>6.4470000000000001</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>6.4459999999999997</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="1">
         <v>6.391</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="1">
         <v>6.3410000000000002</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="1">
         <v>6.3090000000000002</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>6.2930000000000001</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="1">
         <v>6.2619999999999996</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <v>6.234</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <v>6.2210000000000001</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="1">
         <v>6.18</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="1">
         <v>6.1779999999999999</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="1">
         <v>6.1719999999999997</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="1">
         <v>6.165</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="1">
         <v>6.1280000000000001</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="1">
         <v>6.125</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>6.1230000000000002</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="1">
         <v>6.12</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="1">
         <v>6.1059999999999999</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="1">
         <v>6.0860000000000003</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="1">
         <v>6.0709999999999997</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>6.0629999999999997</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>6.0389999999999997</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="1">
         <v>6.0220000000000002</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="1">
         <v>6.016</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>5.9669999999999996</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>5.9480000000000004</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="1">
         <v>5.9349999999999996</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="1">
         <v>5.9039999999999999</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>5.891</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="1">
         <v>5.8570000000000002</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="1">
         <v>5.85</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="1">
         <v>5.8280000000000003</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="1">
         <v>5.8209999999999997</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>5.7809999999999997</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="1">
         <v>5.7679999999999998</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="1">
         <v>5.7610000000000001</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="1">
         <v>5.7370000000000001</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="1">
         <v>5.7110000000000003</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="1">
         <v>5.6</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <v>5.585</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="1">
         <v>5.5780000000000003</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>5.5590000000000002</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>5.5469999999999997</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="1">
         <v>5.5330000000000004</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="1">
         <v>5.4850000000000003</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="1">
         <v>5.4740000000000002</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="1">
         <v>5.4669999999999996</v>
       </c>
-      <c r="C82" s="2"/>
+      <c r="C82" s="1"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>5.4589999999999996</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="1">
         <v>5.4249999999999998</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="1">
         <v>5.399</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="1">
         <v>5.3769999999999998</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="1">
         <v>5.3769999999999998</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="1">
         <v>5.3710000000000004</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="1">
         <v>5.33</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="1">
         <v>5.24</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="1">
         <v>5.2350000000000003</v>
       </c>
-      <c r="C91" s="2"/>
+      <c r="C91" s="1"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="1">
         <v>5.1989999999999998</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="1">
         <v>5.1989999999999998</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="1">
         <v>5.194</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="1">
         <v>5.173</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="1">
         <v>5.1639999999999997</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="1">
         <v>5.1550000000000002</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="1">
         <v>5.14</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="1">
         <v>5.1219999999999999</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="1">
         <v>5.1219999999999999</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="1">
         <v>5.0839999999999996</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="1">
         <v>5.0750000000000002</v>
       </c>
-      <c r="C102" s="2"/>
+      <c r="C102" s="1"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="1">
         <v>5.0599999999999996</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="1">
         <v>5.048</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="1">
         <v>5.048</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="1">
         <v>5.0460000000000003</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="1">
         <v>5.0030000000000001</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="1">
         <v>4.9729999999999999</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="1">
         <v>4.9580000000000002</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="1">
         <v>4.9409999999999998</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="1">
         <v>4.9249999999999998</v>
       </c>
-      <c r="C111" s="2"/>
+      <c r="C111" s="1"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="1">
         <v>4.891</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="1">
         <v>4.8879999999999999</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="1">
         <v>4.8719999999999999</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="1">
         <v>4.7439999999999998</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="1">
         <v>4.67</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="1">
         <v>4.6399999999999997</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="1">
         <v>4.6230000000000002</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="1">
         <v>4.609</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="1">
         <v>4.6029999999999998</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="1">
         <v>4.5519999999999996</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="1">
         <v>4.5430000000000001</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="1">
         <v>4.516</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="1">
         <v>4.516</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="1">
         <v>4.4829999999999997</v>
       </c>
-      <c r="C125" s="2"/>
+      <c r="C125" s="1"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="1">
         <v>4.4790000000000001</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="1">
         <v>4.4589999999999996</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="1">
         <v>4.3959999999999999</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="1">
         <v>4.3940000000000001</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="1">
         <v>4.3620000000000001</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="1">
         <v>4.3390000000000004</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="1">
         <v>4.2880000000000003</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="1">
         <v>4.2510000000000003</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="1">
         <v>4.2409999999999997</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="1">
         <v>4.1970000000000001</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="1">
         <v>4.1529999999999996</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="1">
         <v>4.1520000000000001</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="1">
         <v>4.1120000000000001</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="1">
         <v>3.7770000000000001</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="1">
         <v>3.76</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="1">
         <v>3.75</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="1">
         <v>3.702</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="1">
         <v>3.5739999999999998</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="1">
         <v>3.512</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="1">
         <v>3.4710000000000001</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="1">
         <v>3.2679999999999998</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147" s="1">
         <v>2.9950000000000001</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="1">
         <v>2.9550000000000001</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="1">
         <v>2.4039999999999999</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="1" t="s">
         <v>102</v>
       </c>
     </row>
